--- a/GATEWAY/A1#111#GESTRIABXX/DM_RIABILITA/FSELink/1.0.0/report-checklist.xlsx
+++ b/GATEWAY/A1#111#GESTRIABXX/DM_RIABILITA/FSELink/1.0.0/report-checklist.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andrea\Documents\UILDM\Accreditamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F78AE37A-27AE-4B7D-9FC9-FCA03EAAD24C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F348580-95CB-4B91-A2BF-AC5F22AC538A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1407" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1407" uniqueCount="483">
   <si>
     <t>COME VALORIZZARE LA CHECKLIST (tab TestCases)</t>
   </si>
@@ -1814,15 +1814,6 @@
     <t>2.16.840.1.113883.2.9.4.1.5.5c34b695f9e2fab39876e31d5316fe05260b8c9995728ade09d806e770ae7df3.a8dea25dc6^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
-    <t>2.16.840.1.113883.2.9.4.1.5.0d26c98a0dd77eb84256827d2a47de75437d61ebd71832bcacee248ad3828791.25ed30b438^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2026-01-20T11:51:24Z</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.4.1.5.5c34b695f9e2fab39876e31d5316fe05260b8c9995728ade09d806e770ae7df3.0152ea019b^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
     <t>2026-01-20T11:51:41Z</t>
   </si>
   <si>
@@ -1838,10 +1829,28 @@
     <t>DM Riabilia Impresa Sociale</t>
   </si>
   <si>
-    <t>subject_application_vendor: GESTRIAB</t>
-  </si>
-  <si>
     <t>L'invio al gateway è asincrono per permettere all'utente di proseguire con la propria attività clinica. Sia l'utente che il backoffice hanno a disposizione una dashboard di tutti i documenti raggruppati per stato. Un schermata con dei log parlanti permettono all'utilizzato di capire l'eventuale errore.  Una volta che l'errore è stato corretto dal medico o dal backoffice, il documento rientra nella coda di firma e di ritrasmissione verso il gateway.</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.4.1.5.0d26c98a0dd77eb84256827d2a47de75437d61ebd71832bcacee248ad3828791.9ea216fc6d^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>subject_application_vendor: DM Riabilita Impresa Sociale</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.4.1.5.5c34b695f9e2fab39876e31d5316fe05260b8c9995728ade09d806e770ae7df3.d3f46de474^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2026-06-17T17:29:12Z</t>
+  </si>
+  <si>
+    <t>2026-06-17T17:08:20Z</t>
+  </si>
+  <si>
+    <t>66b68bdd8f031107894c03c284aede9f</t>
+  </si>
+  <si>
+    <t>5478b5671b3d656a0b674fa893297123</t>
   </si>
 </sst>
 </file>
@@ -3913,7 +3922,7 @@
     <col min="5" max="5" width="104.85546875" customWidth="1"/>
     <col min="6" max="7" width="33.140625" customWidth="1"/>
     <col min="8" max="8" width="36.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="33.140625" customWidth="1"/>
+    <col min="9" max="9" width="151.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="27.140625" customWidth="1"/>
     <col min="11" max="11" width="53.42578125" bestFit="1" customWidth="1"/>
     <col min="12" max="18" width="36.42578125" customWidth="1"/>
@@ -3951,7 +3960,7 @@
       </c>
       <c r="B2" s="50"/>
       <c r="C2" s="51" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="D2" s="50"/>
       <c r="F2" s="6"/>
@@ -4005,7 +4014,7 @@
       <c r="A4" s="54"/>
       <c r="B4" s="55"/>
       <c r="C4" s="58" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D4" s="50"/>
       <c r="E4" s="4"/>
@@ -5064,7 +5073,7 @@
         <v>64</v>
       </c>
       <c r="S31" s="38" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="T31" s="38"/>
       <c r="U31" s="39" t="s">
@@ -8407,7 +8416,7 @@
         <v>64</v>
       </c>
       <c r="S116" s="38" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="T116" s="38"/>
       <c r="U116" s="39"/>
@@ -8466,7 +8475,7 @@
         <v>64</v>
       </c>
       <c r="S117" s="38" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="T117" s="38"/>
       <c r="U117" s="39"/>
@@ -8525,7 +8534,7 @@
         <v>64</v>
       </c>
       <c r="S118" s="38" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="T118" s="38"/>
       <c r="U118" s="39"/>
@@ -8584,7 +8593,7 @@
         <v>64</v>
       </c>
       <c r="S119" s="38" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="T119" s="38"/>
       <c r="U119" s="39"/>
@@ -8643,7 +8652,7 @@
         <v>64</v>
       </c>
       <c r="S120" s="38" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="T120" s="38"/>
       <c r="U120" s="39"/>
@@ -8702,7 +8711,7 @@
         <v>64</v>
       </c>
       <c r="S121" s="38" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="T121" s="38"/>
       <c r="U121" s="39"/>
@@ -8761,7 +8770,7 @@
         <v>64</v>
       </c>
       <c r="S122" s="38" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="T122" s="38"/>
       <c r="U122" s="39"/>
@@ -8820,7 +8829,7 @@
         <v>64</v>
       </c>
       <c r="S123" s="38" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="T123" s="38"/>
       <c r="U123" s="39"/>
@@ -8879,7 +8888,7 @@
         <v>64</v>
       </c>
       <c r="S124" s="38" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="T124" s="38"/>
       <c r="U124" s="39"/>
@@ -8938,7 +8947,7 @@
         <v>64</v>
       </c>
       <c r="S125" s="38" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="T125" s="38"/>
       <c r="U125" s="39"/>
@@ -8997,7 +9006,7 @@
         <v>64</v>
       </c>
       <c r="S126" s="38" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="T126" s="38"/>
       <c r="U126" s="39"/>
@@ -9056,7 +9065,7 @@
         <v>64</v>
       </c>
       <c r="S127" s="38" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="T127" s="38"/>
       <c r="U127" s="39"/>
@@ -9115,7 +9124,7 @@
         <v>64</v>
       </c>
       <c r="S128" s="38" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="T128" s="38"/>
       <c r="U128" s="39"/>
@@ -9174,7 +9183,7 @@
         <v>64</v>
       </c>
       <c r="S129" s="38" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="T129" s="38"/>
       <c r="U129" s="39"/>
@@ -9233,7 +9242,7 @@
         <v>64</v>
       </c>
       <c r="S130" s="38" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="T130" s="38"/>
       <c r="U130" s="39"/>
@@ -10546,16 +10555,16 @@
         <v>379</v>
       </c>
       <c r="F164" s="37">
-        <v>46042</v>
+        <v>46190</v>
       </c>
       <c r="G164" s="37" t="s">
-        <v>452</v>
+        <v>480</v>
       </c>
       <c r="H164" s="37" t="s">
-        <v>442</v>
+        <v>482</v>
       </c>
       <c r="I164" s="42" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="J164" s="38" t="s">
         <v>64</v>
@@ -10579,7 +10588,7 @@
         <v>64</v>
       </c>
       <c r="S164" s="38" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="T164" s="38"/>
       <c r="U164" s="39"/>
@@ -10605,16 +10614,16 @@
         <v>380</v>
       </c>
       <c r="F165" s="37">
-        <v>46042</v>
+        <v>46190</v>
       </c>
       <c r="G165" s="37" t="s">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="H165" s="37" t="s">
-        <v>442</v>
+        <v>481</v>
       </c>
       <c r="I165" s="42" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="J165" s="38" t="s">
         <v>64</v>
@@ -10638,7 +10647,7 @@
         <v>64</v>
       </c>
       <c r="S165" s="38" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="T165" s="38"/>
       <c r="U165" s="39"/>
@@ -11057,13 +11066,13 @@
         <v>46042</v>
       </c>
       <c r="G176" s="35" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="H176" s="35" t="s">
         <v>442</v>
       </c>
       <c r="I176" s="35" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="J176" s="38" t="s">
         <v>64</v>
@@ -11087,7 +11096,7 @@
         <v>64</v>
       </c>
       <c r="S176" s="38" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="T176" s="38"/>
       <c r="U176" s="35"/>
@@ -11350,13 +11359,13 @@
         <v>46042</v>
       </c>
       <c r="G183" s="35" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="H183" s="35" t="s">
         <v>442</v>
       </c>
       <c r="I183" s="35" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="J183" s="38" t="s">
         <v>64</v>
@@ -11380,7 +11389,7 @@
         <v>64</v>
       </c>
       <c r="S183" s="38" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="T183" s="38"/>
       <c r="U183" s="35"/>
@@ -11649,7 +11658,7 @@
         <v>442</v>
       </c>
       <c r="I190" s="42" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="J190" s="38" t="s">
         <v>64</v>
@@ -11673,7 +11682,7 @@
         <v>64</v>
       </c>
       <c r="S190" s="38" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="T190" s="38"/>
       <c r="U190" s="39"/>
